--- a/49898_Cuenca_Crisnejas/_raw_reportes_xlsx/IDConfig_65032_completo.xlsx
+++ b/49898_Cuenca_Crisnejas/_raw_reportes_xlsx/IDConfig_65032_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rd6dbbb7d0c2f4d49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rdd90204e14934e38"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,16 +255,526 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3306</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3306</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3757</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3757</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3306</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3306</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3306</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3306</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3757</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4768</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4768</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4768</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4768</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6608</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6608</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6608</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6608</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4768</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4768</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4768</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4244</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4244</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4244</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4768</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4244</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>15/08/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
         <x:is>
-          <x:t>14:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.4459</x:v>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4244</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -275,11 +785,11 @@
       </x:c>
       <x:c s="7" t="inlineStr">
         <x:is>
-          <x:t>10:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.4991</x:v>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4244</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -290,11 +800,26 @@
       </x:c>
       <x:c s="7" t="inlineStr">
         <x:is>
-          <x:t>06:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.4991</x:v>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4768</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4768</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -309,7 +834,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4459</x:v>
+        <x:v>      0.4244</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -324,7 +849,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4991</x:v>
+        <x:v>      0.4768</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -339,7 +864,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4991</x:v>
+        <x:v>      0.4768</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -354,7 +879,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3421</x:v>
+        <x:v>      0.3306</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -369,7 +894,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3935</x:v>
+        <x:v>      0.3757</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -384,7 +909,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3935</x:v>
+        <x:v>      0.3757</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -399,7 +924,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3935</x:v>
+        <x:v>      0.3757</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -414,7 +939,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3935</x:v>
+        <x:v>      0.3757</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -429,7 +954,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3935</x:v>
+        <x:v>      0.3757</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -444,7 +969,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3935</x:v>
+        <x:v>      0.3757</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -459,7 +984,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -474,7 +999,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -489,7 +1014,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -504,7 +1029,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -519,7 +1044,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -534,7 +1059,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3421</x:v>
+        <x:v>      0.3306</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -549,7 +1074,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3421</x:v>
+        <x:v>      0.3306</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -564,7 +1089,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3421</x:v>
+        <x:v>      0.3306</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -579,7 +1104,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -594,7 +1119,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -609,7 +1134,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -624,7 +1149,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -639,7 +1164,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -654,7 +1179,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2418</x:v>
+        <x:v>      0.2515</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -669,7 +1194,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -684,7 +1209,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -699,7 +1224,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -714,7 +1239,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -729,7 +1254,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -744,7 +1269,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -759,7 +1284,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -774,7 +1299,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -789,7 +1314,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2418</x:v>
+        <x:v>      0.2515</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -804,7 +1329,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2418</x:v>
+        <x:v>      0.2515</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -819,7 +1344,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -834,7 +1359,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -849,7 +1374,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1931</x:v>
+        <x:v>      0.2175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -864,7 +1389,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1931</x:v>
+        <x:v>      0.2175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -879,7 +1404,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1931</x:v>
+        <x:v>      0.2175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -894,7 +1419,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1931</x:v>
+        <x:v>      0.2175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -909,7 +1434,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1931</x:v>
+        <x:v>      0.2175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -924,7 +1449,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1931</x:v>
+        <x:v>      0.2175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -939,7 +1464,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1931</x:v>
+        <x:v>      0.2175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -954,7 +1479,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1931</x:v>
+        <x:v>      0.2175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -969,7 +1494,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -984,7 +1509,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3421</x:v>
+        <x:v>      0.3306</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -999,7 +1524,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3421</x:v>
+        <x:v>      0.3306</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1014,7 +1539,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3421</x:v>
+        <x:v>      0.3306</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1029,7 +1554,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1044,7 +1569,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1059,7 +1584,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1074,7 +1599,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1089,7 +1614,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2418</x:v>
+        <x:v>      0.2515</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1104,7 +1629,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1119,7 +1644,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1134,7 +1659,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1149,7 +1674,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1164,7 +1689,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3935</x:v>
+        <x:v>      0.3757</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1179,7 +1704,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3935</x:v>
+        <x:v>      0.3757</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1194,7 +1719,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3935</x:v>
+        <x:v>      0.3757</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1209,7 +1734,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3935</x:v>
+        <x:v>      0.3757</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1224,7 +1749,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1239,7 +1764,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1254,7 +1779,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1269,7 +1794,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3935</x:v>
+        <x:v>      0.3757</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1284,7 +1809,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3935</x:v>
+        <x:v>      0.3757</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1299,7 +1824,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3935</x:v>
+        <x:v>      0.3757</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1314,7 +1839,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3935</x:v>
+        <x:v>      0.3757</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1329,7 +1854,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4459</x:v>
+        <x:v>      0.4244</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1344,7 +1869,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4459</x:v>
+        <x:v>      0.4244</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1359,7 +1884,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4459</x:v>
+        <x:v>      0.4244</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1374,7 +1899,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4459</x:v>
+        <x:v>      0.4244</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1389,7 +1914,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4991</x:v>
+        <x:v>      0.4768</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1404,7 +1929,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4991</x:v>
+        <x:v>      0.4768</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1419,7 +1944,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4991</x:v>
+        <x:v>      0.4768</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1434,7 +1959,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4991</x:v>
+        <x:v>      0.4768</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1449,7 +1974,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4991</x:v>
+        <x:v>      0.4768</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1464,7 +1989,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4991</x:v>
+        <x:v>      0.4768</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1479,7 +2004,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4991</x:v>
+        <x:v>      0.4768</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1494,7 +2019,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.5981</x:v>
+        <x:v>      0.5928</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1509,7 +2034,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.5981</x:v>
+        <x:v>      0.5928</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1524,7 +2049,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.5981</x:v>
+        <x:v>      0.5928</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1539,7 +2064,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.5981</x:v>
+        <x:v>      0.5928</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1554,7 +2079,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.5981</x:v>
+        <x:v>      0.5928</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1569,7 +2094,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3421</x:v>
+        <x:v>      0.3306</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1584,7 +2109,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3421</x:v>
+        <x:v>      0.3306</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1599,7 +2124,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3421</x:v>
+        <x:v>      0.3306</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1614,7 +2139,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3421</x:v>
+        <x:v>      0.3306</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1629,7 +2154,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1644,7 +2169,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1659,7 +2184,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1674,7 +2199,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1689,7 +2214,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2418</x:v>
+        <x:v>      0.2515</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1704,7 +2229,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2418</x:v>
+        <x:v>      0.2515</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1719,7 +2244,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1931</x:v>
+        <x:v>      0.2175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1734,7 +2259,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1931</x:v>
+        <x:v>      0.2175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1749,7 +2274,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3421</x:v>
+        <x:v>      0.3306</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1764,7 +2289,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3421</x:v>
+        <x:v>      0.3306</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1779,7 +2304,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3935</x:v>
+        <x:v>      0.3757</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1794,7 +2319,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3935</x:v>
+        <x:v>      0.3757</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1809,7 +2334,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3421</x:v>
+        <x:v>      0.3306</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1824,7 +2349,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1839,7 +2364,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1854,7 +2379,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1869,7 +2394,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1884,7 +2409,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3421</x:v>
+        <x:v>      0.3306</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1899,7 +2424,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3935</x:v>
+        <x:v>      0.3757</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1914,7 +2439,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3935</x:v>
+        <x:v>      0.3757</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1929,7 +2454,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3421</x:v>
+        <x:v>      0.3306</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1944,7 +2469,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3421</x:v>
+        <x:v>      0.3306</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1959,7 +2484,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2418</x:v>
+        <x:v>      0.2515</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1974,7 +2499,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2418</x:v>
+        <x:v>      0.2515</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1989,7 +2514,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2004,7 +2529,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2019,7 +2544,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1931</x:v>
+        <x:v>      0.2175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2034,7 +2559,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1931</x:v>
+        <x:v>      0.2175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2049,7 +2574,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3421</x:v>
+        <x:v>      0.3306</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2064,7 +2589,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3421</x:v>
+        <x:v>      0.3306</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2079,7 +2604,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3421</x:v>
+        <x:v>      0.3306</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2094,7 +2619,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3421</x:v>
+        <x:v>      0.3306</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2109,7 +2634,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2124,7 +2649,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2139,7 +2664,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2154,7 +2679,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2169,7 +2694,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1931</x:v>
+        <x:v>      0.2175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2184,7 +2709,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2199,7 +2724,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2418</x:v>
+        <x:v>      0.2515</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2214,7 +2739,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2418</x:v>
+        <x:v>      0.2515</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2229,7 +2754,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2418</x:v>
+        <x:v>      0.2515</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2244,7 +2769,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2418</x:v>
+        <x:v>      0.2515</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2259,7 +2784,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1931</x:v>
+        <x:v>      0.2175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2274,7 +2799,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1931</x:v>
+        <x:v>      0.2175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2289,7 +2814,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1931</x:v>
+        <x:v>      0.2175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2304,7 +2829,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2319,7 +2844,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2334,7 +2859,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3421</x:v>
+        <x:v>      0.3306</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2349,7 +2874,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2364,7 +2889,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2418</x:v>
+        <x:v>      0.2515</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2379,7 +2904,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1931</x:v>
+        <x:v>      0.2175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2394,7 +2919,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1931</x:v>
+        <x:v>      0.2175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2409,7 +2934,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1931</x:v>
+        <x:v>      0.2175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2424,7 +2949,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1931</x:v>
+        <x:v>      0.2175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2439,7 +2964,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1931</x:v>
+        <x:v>      0.2175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2454,7 +2979,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1931</x:v>
+        <x:v>      0.2175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2469,7 +2994,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1931</x:v>
+        <x:v>      0.2175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2484,7 +3009,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2418</x:v>
+        <x:v>      0.2515</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2499,7 +3024,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2418</x:v>
+        <x:v>      0.2515</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2514,7 +3039,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2418</x:v>
+        <x:v>      0.2515</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2529,7 +3054,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2544,7 +3069,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2559,7 +3084,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2574,7 +3099,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2589,7 +3114,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2418</x:v>
+        <x:v>      0.2515</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2604,7 +3129,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2418</x:v>
+        <x:v>      0.2515</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2619,7 +3144,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2418</x:v>
+        <x:v>      0.2515</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2634,7 +3159,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2418</x:v>
+        <x:v>      0.2515</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2649,7 +3174,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2664,7 +3189,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2679,7 +3204,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2694,7 +3219,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2709,7 +3234,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1931</x:v>
+        <x:v>      0.2175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2724,7 +3249,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1931</x:v>
+        <x:v>      0.2175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2739,7 +3264,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1931</x:v>
+        <x:v>      0.2175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2754,7 +3279,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.1931</x:v>
+        <x:v>      0.2175</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2769,7 +3294,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3421</x:v>
+        <x:v>      0.3306</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2784,7 +3309,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3935</x:v>
+        <x:v>      0.3757</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2799,7 +3324,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3421</x:v>
+        <x:v>      0.3306</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2814,7 +3339,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2829,7 +3354,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2844,7 +3369,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2859,7 +3384,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.2915</x:v>
+        <x:v>      0.2892</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2874,7 +3399,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3421</x:v>
+        <x:v>      0.3306</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2889,7 +3414,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.5981</x:v>
+        <x:v>      0.5928</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2904,7 +3429,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.5981</x:v>
+        <x:v>      0.5928</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2919,7 +3444,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.5981</x:v>
+        <x:v>      0.5928</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2934,7 +3459,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.5981</x:v>
+        <x:v>      0.5928</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2949,7 +3474,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.5981</x:v>
+        <x:v>      0.5928</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2964,7 +3489,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.5981</x:v>
+        <x:v>      0.5928</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2979,7 +3504,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.5981</x:v>
+        <x:v>      0.5928</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2994,7 +3519,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.5981</x:v>
+        <x:v>      0.5928</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3069,7 +3594,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.5533</x:v>
+        <x:v>      0.5330</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3129,7 +3654,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.5981</x:v>
+        <x:v>      0.5928</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3144,7 +3669,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4459</x:v>
+        <x:v>      0.4244</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3159,7 +3684,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4459</x:v>
+        <x:v>      0.4244</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3174,7 +3699,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4459</x:v>
+        <x:v>      0.4244</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3189,7 +3714,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.5981</x:v>
+        <x:v>      0.5928</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3249,7 +3774,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.5533</x:v>
+        <x:v>      0.5330</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3489,7 +4014,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4459</x:v>
+        <x:v>      0.4244</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3504,7 +4029,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4459</x:v>
+        <x:v>      0.4244</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3519,7 +4044,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4991</x:v>
+        <x:v>      0.4768</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3534,7 +4059,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4991</x:v>
+        <x:v>      0.4768</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3549,7 +4074,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3935</x:v>
+        <x:v>      0.3757</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3564,7 +4089,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3935</x:v>
+        <x:v>      0.3757</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3579,7 +4104,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3935</x:v>
+        <x:v>      0.3757</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3594,7 +4119,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3935</x:v>
+        <x:v>      0.3757</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3609,7 +4134,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4991</x:v>
+        <x:v>      0.4768</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3624,7 +4149,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4991</x:v>
+        <x:v>      0.4768</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3639,7 +4164,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4991</x:v>
+        <x:v>      0.4768</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3654,7 +4179,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.4991</x:v>
+        <x:v>      0.4768</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3669,7 +4194,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.3935</x:v>
+        <x:v>      0.3757</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3684,7 +4209,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.5981</x:v>
+        <x:v>      0.5928</x:v>
       </x:c>
     </x:row>
     <x:row>

--- a/49898_Cuenca_Crisnejas/_raw_reportes_xlsx/IDConfig_65032_completo.xlsx
+++ b/49898_Cuenca_Crisnejas/_raw_reportes_xlsx/IDConfig_65032_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rdd90204e14934e38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rdf4bb2473f34499f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,12 +255,2877 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>11/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2175</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3306</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3757</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3757</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6991</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3306</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3306</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3306</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3306</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3757</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3757</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3757</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3757</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4768</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4768</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4768</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5330</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3306</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3306</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6608</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6991</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      2.8522</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2175</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2175</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2175</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2175</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2175</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2175</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2175</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2175</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5928</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6608</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3306</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3306</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3757</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3757</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3757</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4768</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5928</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5928</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.6271</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3757</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3757</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3757</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3757</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3757</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3757</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3757</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3757</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3306</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3306</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3306</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3306</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3757</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1605</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1605</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1605</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1605</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1872</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1872</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1872</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1872</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1872</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1872</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1872</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1872</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1872</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1872</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1872</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1872</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1872</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1872</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1872</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1872</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1872</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1872</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1872</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.1376</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2175</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2175</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2175</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2515</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3306</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3306</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3306</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3306</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4244</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4768</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4768</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4768</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4768</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4768</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4768</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4768</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3757</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4768</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4768</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5330</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3757</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3757</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3757</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3757</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4768</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4768</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4768</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4768</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4768</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4768</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4768</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4768</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3757</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4768</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4768</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.5928</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.2892</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3306</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4244</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3757</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4768</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4768</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4768</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4244</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3757</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3757</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3757</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>24/08/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
         <x:is>
-          <x:t>10:00</x:t>
+          <x:t>18:00</x:t>
         </x:is>
       </x:c>
       <x:c s="3">
@@ -275,11 +3140,41 @@
       </x:c>
       <x:c s="7" t="inlineStr">
         <x:is>
-          <x:t>06:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      0.2892</x:v>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.3306</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4768</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.4768</x:v>
       </x:c>
     </x:row>
     <x:row>
